--- a/北京中心顾问薪酬绩效台账_v4.xlsx
+++ b/北京中心顾问薪酬绩效台账_v4.xlsx
@@ -38436,7 +38436,7 @@
         <v>600</v>
       </c>
       <c r="H3" s="41">
-        <f>Q3+U3</f>
+        <f>Q3</f>
         <v/>
       </c>
       <c r="I3" s="41" t="n">
@@ -38541,9 +38541,8 @@
       <c r="G4" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="41">
-        <f>Q4+U4</f>
-        <v/>
+      <c r="H4" s="41" t="n">
+        <v>27810.468</v>
       </c>
       <c r="I4" s="41" t="n">
         <v>510000</v>
@@ -38647,9 +38646,8 @@
       <c r="G5" s="41" t="n">
         <v>1200</v>
       </c>
-      <c r="H5" s="41">
-        <f>Q5+U5</f>
-        <v/>
+      <c r="H5" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="I5" s="41" t="n">
         <v>510000</v>
@@ -38915,81 +38913,31 @@
       <c r="AR7" s="37" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="52" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>赵星火</t>
-        </is>
-      </c>
-      <c r="C8" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D8" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E8" s="53" t="inlineStr">
-        <is>
-          <t>O2级学习顾问</t>
-        </is>
-      </c>
-      <c r="F8" s="54">
-        <f>G8+H8</f>
-        <v/>
-      </c>
-      <c r="G8" s="54" t="n">
-        <v>920</v>
-      </c>
-      <c r="H8" s="54">
-        <f>Q8+U8</f>
-        <v/>
-      </c>
-      <c r="I8" s="54" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="J8" s="54" t="n"/>
-      <c r="K8" s="54" t="n">
-        <v>1282149.75</v>
-      </c>
-      <c r="L8" s="54" t="n"/>
-      <c r="M8" s="54" t="n">
-        <v>64386.17000000001</v>
-      </c>
-      <c r="N8" s="54" t="n">
-        <v>1346535.92</v>
-      </c>
-      <c r="O8" s="55" t="n">
-        <v>1.22412356363636</v>
-      </c>
-      <c r="P8" s="55" t="n">
-        <v>0.04000000000000001</v>
-      </c>
-      <c r="Q8" s="62" t="n">
-        <v>53861.4368</v>
-      </c>
-      <c r="R8" s="54" t="n"/>
-      <c r="S8" s="54" t="n"/>
-      <c r="T8" s="55" t="n"/>
-      <c r="U8" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="54" t="n">
-        <v>92</v>
-      </c>
-      <c r="W8" s="54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X8" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="54" t="n">
-        <v>920</v>
-      </c>
+      <c r="A8" s="43" t="n"/>
+      <c r="B8" s="38" t="n"/>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="44" t="n"/>
+      <c r="G8" s="44" t="n"/>
+      <c r="H8" s="44" t="n"/>
+      <c r="I8" s="44" t="n"/>
+      <c r="J8" s="44" t="n"/>
+      <c r="K8" s="44" t="n"/>
+      <c r="L8" s="44" t="n"/>
+      <c r="M8" s="44" t="n"/>
+      <c r="N8" s="44" t="n"/>
+      <c r="O8" s="45" t="n"/>
+      <c r="P8" s="45" t="n"/>
+      <c r="Q8" s="48" t="n"/>
+      <c r="R8" s="44" t="n"/>
+      <c r="S8" s="44" t="n"/>
+      <c r="T8" s="48" t="n"/>
+      <c r="U8" s="48" t="n"/>
+      <c r="V8" s="44" t="n"/>
+      <c r="W8" s="44" t="n"/>
+      <c r="X8" s="45" t="n"/>
+      <c r="Y8" s="44" t="n"/>
       <c r="Z8" s="37" t="n"/>
       <c r="AA8" s="37" t="n"/>
       <c r="AB8" s="37" t="n"/>
@@ -39011,81 +38959,31 @@
       <c r="AR8" s="37" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="52" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B9" s="53" t="inlineStr">
-        <is>
-          <t>谭悦</t>
-        </is>
-      </c>
-      <c r="C9" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D9" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E9" s="53" t="inlineStr">
-        <is>
-          <t>O3级学习顾问</t>
-        </is>
-      </c>
-      <c r="F9" s="54">
-        <f>G9+H9</f>
-        <v/>
-      </c>
-      <c r="G9" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="54">
-        <f>Q9+U9</f>
-        <v/>
-      </c>
-      <c r="I9" s="54" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="J9" s="54" t="n"/>
-      <c r="K9" s="54" t="n">
-        <v>1781563.85</v>
-      </c>
-      <c r="L9" s="54" t="n"/>
-      <c r="M9" s="54" t="n">
-        <v>103852.6</v>
-      </c>
-      <c r="N9" s="54" t="n">
-        <v>1885416.45</v>
-      </c>
-      <c r="O9" s="55" t="n">
-        <v>1.71401495454545</v>
-      </c>
-      <c r="P9" s="55" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q9" s="62" t="n">
-        <v>94270.82249999999</v>
-      </c>
-      <c r="R9" s="54" t="n"/>
-      <c r="S9" s="54" t="n"/>
-      <c r="T9" s="55" t="n"/>
-      <c r="U9" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="54" t="n">
-        <v>100</v>
-      </c>
-      <c r="W9" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="55" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Y9" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="A9" s="43" t="n"/>
+      <c r="B9" s="38" t="n"/>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="38" t="n"/>
+      <c r="E9" s="38" t="n"/>
+      <c r="F9" s="44" t="n"/>
+      <c r="G9" s="44" t="n"/>
+      <c r="H9" s="44" t="n"/>
+      <c r="I9" s="44" t="n"/>
+      <c r="J9" s="44" t="n"/>
+      <c r="K9" s="44" t="n"/>
+      <c r="L9" s="44" t="n"/>
+      <c r="M9" s="44" t="n"/>
+      <c r="N9" s="44" t="n"/>
+      <c r="O9" s="45" t="n"/>
+      <c r="P9" s="45" t="n"/>
+      <c r="Q9" s="38" t="n"/>
+      <c r="R9" s="44" t="n"/>
+      <c r="S9" s="44" t="n"/>
+      <c r="T9" s="38" t="n"/>
+      <c r="U9" s="38" t="n"/>
+      <c r="V9" s="44" t="n"/>
+      <c r="W9" s="44" t="n"/>
+      <c r="X9" s="45" t="n"/>
+      <c r="Y9" s="44" t="n"/>
       <c r="Z9" s="37" t="n"/>
       <c r="AA9" s="37" t="n"/>
       <c r="AB9" s="37" t="n"/>
@@ -39107,63 +39005,31 @@
       <c r="AR9" s="37" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="52" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t>李涛</t>
-        </is>
-      </c>
-      <c r="C10" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E10" s="53" t="inlineStr">
-        <is>
-          <t>O1级学习顾问</t>
-        </is>
-      </c>
-      <c r="F10" s="54">
-        <f>G10+H10</f>
-        <v/>
-      </c>
-      <c r="G10" s="54" t="n">
-        <v>1548.38709677419</v>
-      </c>
-      <c r="H10" s="54">
-        <f>Q10+U10</f>
-        <v/>
-      </c>
-      <c r="I10" s="54" t="n"/>
-      <c r="J10" s="54" t="n"/>
-      <c r="K10" s="54" t="n"/>
-      <c r="L10" s="54" t="n"/>
-      <c r="M10" s="54" t="n"/>
-      <c r="N10" s="54" t="n"/>
-      <c r="O10" s="55" t="n"/>
-      <c r="P10" s="55" t="n"/>
-      <c r="Q10" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="54" t="n"/>
-      <c r="S10" s="54" t="n"/>
-      <c r="T10" s="55" t="n"/>
-      <c r="U10" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="54" t="n"/>
-      <c r="W10" s="54" t="n"/>
-      <c r="X10" s="55" t="n"/>
-      <c r="Y10" s="54" t="n">
-        <v>1548.38709677419</v>
-      </c>
+      <c r="A10" s="43" t="n"/>
+      <c r="B10" s="38" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="38" t="n"/>
+      <c r="F10" s="44" t="n"/>
+      <c r="G10" s="44" t="n"/>
+      <c r="H10" s="44" t="n"/>
+      <c r="I10" s="44" t="n"/>
+      <c r="J10" s="44" t="n"/>
+      <c r="K10" s="44" t="n"/>
+      <c r="L10" s="44" t="n"/>
+      <c r="M10" s="44" t="n"/>
+      <c r="N10" s="44" t="n"/>
+      <c r="O10" s="45" t="n"/>
+      <c r="P10" s="45" t="n"/>
+      <c r="Q10" s="38" t="n"/>
+      <c r="R10" s="44" t="n"/>
+      <c r="S10" s="44" t="n"/>
+      <c r="T10" s="38" t="n"/>
+      <c r="U10" s="38" t="n"/>
+      <c r="V10" s="44" t="n"/>
+      <c r="W10" s="44" t="n"/>
+      <c r="X10" s="45" t="n"/>
+      <c r="Y10" s="44" t="n"/>
       <c r="Z10" s="37" t="n"/>
       <c r="AA10" s="37" t="n"/>
       <c r="AB10" s="37" t="n"/>
@@ -39185,85 +39051,31 @@
       <c r="AR10" s="37" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="52" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B11" s="53" t="inlineStr">
-        <is>
-          <t>赵星火</t>
-        </is>
-      </c>
-      <c r="C11" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D11" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E11" s="53" t="inlineStr">
-        <is>
-          <t>O2级学习顾问</t>
-        </is>
-      </c>
-      <c r="F11" s="54">
-        <f>G11+H11</f>
-        <v/>
-      </c>
-      <c r="G11" s="54" t="n">
-        <v>700</v>
-      </c>
-      <c r="H11" s="54">
-        <f>Q11+U11</f>
-        <v/>
-      </c>
-      <c r="I11" s="54" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J11" s="54" t="n">
-        <v>750000</v>
-      </c>
-      <c r="K11" s="54" t="n">
-        <v>938072.85</v>
-      </c>
-      <c r="L11" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="54" t="n">
-        <v>26001.5</v>
-      </c>
-      <c r="N11" s="54" t="n">
-        <v>964074.35</v>
-      </c>
-      <c r="O11" s="55" t="n">
-        <v>1.28543246666667</v>
-      </c>
-      <c r="P11" s="55" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Q11" s="62" t="n">
-        <v>38562.974</v>
-      </c>
-      <c r="R11" s="54" t="n"/>
-      <c r="S11" s="54" t="n"/>
-      <c r="T11" s="55" t="n"/>
-      <c r="U11" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="54" t="n">
-        <v>70</v>
-      </c>
-      <c r="W11" s="54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X11" s="55" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Y11" s="54" t="n">
-        <v>700</v>
-      </c>
+      <c r="A11" s="43" t="n"/>
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="38" t="n"/>
+      <c r="F11" s="44" t="n"/>
+      <c r="G11" s="44" t="n"/>
+      <c r="H11" s="44" t="n"/>
+      <c r="I11" s="44" t="n"/>
+      <c r="J11" s="44" t="n"/>
+      <c r="K11" s="44" t="n"/>
+      <c r="L11" s="44" t="n"/>
+      <c r="M11" s="44" t="n"/>
+      <c r="N11" s="44" t="n"/>
+      <c r="O11" s="45" t="n"/>
+      <c r="P11" s="45" t="n"/>
+      <c r="Q11" s="38" t="n"/>
+      <c r="R11" s="44" t="n"/>
+      <c r="S11" s="44" t="n"/>
+      <c r="T11" s="38" t="n"/>
+      <c r="U11" s="38" t="n"/>
+      <c r="V11" s="44" t="n"/>
+      <c r="W11" s="44" t="n"/>
+      <c r="X11" s="45" t="n"/>
+      <c r="Y11" s="44" t="n"/>
       <c r="Z11" s="37" t="n"/>
       <c r="AA11" s="37" t="n"/>
       <c r="AB11" s="37" t="n"/>
@@ -39285,83 +39097,31 @@
       <c r="AR11" s="37" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="52" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t>谭悦</t>
-        </is>
-      </c>
-      <c r="C12" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D12" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E12" s="53" t="inlineStr">
-        <is>
-          <t>O3级学习顾问</t>
-        </is>
-      </c>
-      <c r="F12" s="54">
-        <f>G12+H12</f>
-        <v/>
-      </c>
-      <c r="G12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="54">
-        <f>Q12+U12</f>
-        <v/>
-      </c>
-      <c r="I12" s="54" t="n">
-        <v>750000</v>
-      </c>
-      <c r="J12" s="54" t="n">
-        <v>750000</v>
-      </c>
-      <c r="K12" s="54" t="n">
-        <v>826786.225</v>
-      </c>
-      <c r="L12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="54" t="n">
-        <v>19372.5</v>
-      </c>
-      <c r="N12" s="54" t="n">
-        <v>846158.725</v>
-      </c>
-      <c r="O12" s="55" t="n">
-        <v>1.12821163333333</v>
-      </c>
-      <c r="P12" s="55" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q12" s="62" t="n">
-        <v>25384.76175</v>
-      </c>
-      <c r="R12" s="54" t="n"/>
-      <c r="S12" s="54" t="n"/>
-      <c r="T12" s="55" t="n"/>
-      <c r="U12" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="54" t="n">
-        <v>90</v>
-      </c>
-      <c r="W12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="55" t="n"/>
-      <c r="Y12" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="A12" s="43" t="n"/>
+      <c r="B12" s="38" t="n"/>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="44" t="n"/>
+      <c r="G12" s="44" t="n"/>
+      <c r="H12" s="44" t="n"/>
+      <c r="I12" s="44" t="n"/>
+      <c r="J12" s="44" t="n"/>
+      <c r="K12" s="44" t="n"/>
+      <c r="L12" s="44" t="n"/>
+      <c r="M12" s="44" t="n"/>
+      <c r="N12" s="44" t="n"/>
+      <c r="O12" s="45" t="n"/>
+      <c r="P12" s="45" t="n"/>
+      <c r="Q12" s="38" t="n"/>
+      <c r="R12" s="44" t="n"/>
+      <c r="S12" s="44" t="n"/>
+      <c r="T12" s="38" t="n"/>
+      <c r="U12" s="38" t="n"/>
+      <c r="V12" s="44" t="n"/>
+      <c r="W12" s="44" t="n"/>
+      <c r="X12" s="45" t="n"/>
+      <c r="Y12" s="44" t="n"/>
       <c r="Z12" s="37" t="n"/>
       <c r="AA12" s="37" t="n"/>
       <c r="AB12" s="37" t="n"/>
@@ -39383,85 +39143,31 @@
       <c r="AR12" s="37" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="52" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B13" s="53" t="inlineStr">
-        <is>
-          <t>李涛</t>
-        </is>
-      </c>
-      <c r="C13" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D13" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E13" s="53" t="inlineStr">
-        <is>
-          <t>O1级学习顾问</t>
-        </is>
-      </c>
-      <c r="F13" s="54">
-        <f>G13+H13</f>
-        <v/>
-      </c>
-      <c r="G13" s="54" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H13" s="54">
-        <f>Q13+U13</f>
-        <v/>
-      </c>
-      <c r="I13" s="54" t="n">
-        <v>100000</v>
-      </c>
-      <c r="J13" s="54" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K13" s="54" t="n">
-        <v>119940</v>
-      </c>
-      <c r="L13" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="54" t="n">
-        <v>19472.5</v>
-      </c>
-      <c r="N13" s="54" t="n">
-        <v>139412.5</v>
-      </c>
-      <c r="O13" s="55" t="n">
-        <v>1.394125</v>
-      </c>
-      <c r="P13" s="55" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q13" s="62" t="n">
-        <v>2788.25</v>
-      </c>
-      <c r="R13" s="54" t="n"/>
-      <c r="S13" s="54" t="n"/>
-      <c r="T13" s="55" t="n"/>
-      <c r="U13" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="54" t="n">
-        <v>90</v>
-      </c>
-      <c r="W13" s="54" t="n">
-        <v>2000</v>
-      </c>
-      <c r="X13" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="54" t="n">
-        <v>2000</v>
-      </c>
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="37" t="n"/>
+      <c r="O13" s="37" t="n"/>
+      <c r="P13" s="37" t="n"/>
+      <c r="Q13" s="37" t="n"/>
+      <c r="R13" s="37" t="n"/>
+      <c r="S13" s="37" t="n"/>
+      <c r="T13" s="37" t="n"/>
+      <c r="U13" s="37" t="n"/>
+      <c r="V13" s="37" t="n"/>
+      <c r="W13" s="37" t="n"/>
+      <c r="X13" s="37" t="n"/>
+      <c r="Y13" s="37" t="n"/>
       <c r="Z13" s="37" t="n"/>
       <c r="AA13" s="37" t="n"/>
       <c r="AB13" s="37" t="n"/>
@@ -39483,85 +39189,31 @@
       <c r="AR13" s="37" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="52" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B14" s="53" t="inlineStr">
-        <is>
-          <t>赵星火</t>
-        </is>
-      </c>
-      <c r="C14" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D14" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E14" s="53" t="inlineStr">
-        <is>
-          <t>O2级学习顾问</t>
-        </is>
-      </c>
-      <c r="F14" s="54">
-        <f>G14+H14</f>
-        <v/>
-      </c>
-      <c r="G14" s="54" t="n">
-        <v>830.45</v>
-      </c>
-      <c r="H14" s="54">
-        <f>Q14+U14</f>
-        <v/>
-      </c>
-      <c r="I14" s="54" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J14" s="54" t="n">
-        <v>680000</v>
-      </c>
-      <c r="K14" s="54" t="n">
-        <v>849025.7000000001</v>
-      </c>
-      <c r="L14" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="54" t="n">
-        <v>62140.7</v>
-      </c>
-      <c r="N14" s="54" t="n">
-        <v>911166.4</v>
-      </c>
-      <c r="O14" s="55" t="n">
-        <v>1.33995058823529</v>
-      </c>
-      <c r="P14" s="55" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Q14" s="62" t="n">
-        <v>36446.656</v>
-      </c>
-      <c r="R14" s="54" t="n"/>
-      <c r="S14" s="54" t="n"/>
-      <c r="T14" s="55" t="n"/>
-      <c r="U14" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="54" t="n">
-        <v>83.045</v>
-      </c>
-      <c r="W14" s="54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X14" s="55" t="n">
-        <v>0.83045</v>
-      </c>
-      <c r="Y14" s="54" t="n">
-        <v>830.45</v>
-      </c>
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="37" t="n"/>
+      <c r="H14" s="37" t="n"/>
+      <c r="I14" s="37" t="n"/>
+      <c r="J14" s="37" t="n"/>
+      <c r="K14" s="37" t="n"/>
+      <c r="L14" s="37" t="n"/>
+      <c r="M14" s="37" t="n"/>
+      <c r="N14" s="37" t="n"/>
+      <c r="O14" s="37" t="n"/>
+      <c r="P14" s="37" t="n"/>
+      <c r="Q14" s="37" t="n"/>
+      <c r="R14" s="37" t="n"/>
+      <c r="S14" s="37" t="n"/>
+      <c r="T14" s="37" t="n"/>
+      <c r="U14" s="37" t="n"/>
+      <c r="V14" s="37" t="n"/>
+      <c r="W14" s="37" t="n"/>
+      <c r="X14" s="37" t="n"/>
+      <c r="Y14" s="37" t="n"/>
       <c r="Z14" s="37" t="n"/>
       <c r="AA14" s="37" t="n"/>
       <c r="AB14" s="37" t="n"/>
@@ -39583,83 +39235,31 @@
       <c r="AR14" s="37" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="52" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B15" s="53" t="inlineStr">
-        <is>
-          <t>谭悦</t>
-        </is>
-      </c>
-      <c r="C15" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D15" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E15" s="53" t="inlineStr">
-        <is>
-          <t>O3级学习顾问</t>
-        </is>
-      </c>
-      <c r="F15" s="54">
-        <f>G15+H15</f>
-        <v/>
-      </c>
-      <c r="G15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="54">
-        <f>Q15+U15</f>
-        <v/>
-      </c>
-      <c r="I15" s="54" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J15" s="54" t="n">
-        <v>680000</v>
-      </c>
-      <c r="K15" s="54" t="n">
-        <v>1217288.65</v>
-      </c>
-      <c r="L15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="54" t="n">
-        <v>96426.2</v>
-      </c>
-      <c r="N15" s="54" t="n">
-        <v>1313714.85</v>
-      </c>
-      <c r="O15" s="55" t="n">
-        <v>1.93193360294118</v>
-      </c>
-      <c r="P15" s="55" t="n">
-        <v>0.04999999999999999</v>
-      </c>
-      <c r="Q15" s="62" t="n">
-        <v>65685.74249999999</v>
-      </c>
-      <c r="R15" s="54" t="n"/>
-      <c r="S15" s="54" t="n"/>
-      <c r="T15" s="55" t="n"/>
-      <c r="U15" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="54" t="n">
-        <v>78.76000000000001</v>
-      </c>
-      <c r="W15" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="55" t="n"/>
-      <c r="Y15" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="37" t="n"/>
+      <c r="F15" s="37" t="n"/>
+      <c r="G15" s="37" t="n"/>
+      <c r="H15" s="37" t="n"/>
+      <c r="I15" s="37" t="n"/>
+      <c r="J15" s="37" t="n"/>
+      <c r="K15" s="37" t="n"/>
+      <c r="L15" s="37" t="n"/>
+      <c r="M15" s="37" t="n"/>
+      <c r="N15" s="37" t="n"/>
+      <c r="O15" s="37" t="n"/>
+      <c r="P15" s="37" t="n"/>
+      <c r="Q15" s="37" t="n"/>
+      <c r="R15" s="37" t="n"/>
+      <c r="S15" s="37" t="n"/>
+      <c r="T15" s="37" t="n"/>
+      <c r="U15" s="37" t="n"/>
+      <c r="V15" s="37" t="n"/>
+      <c r="W15" s="37" t="n"/>
+      <c r="X15" s="37" t="n"/>
+      <c r="Y15" s="37" t="n"/>
       <c r="Z15" s="37" t="n"/>
       <c r="AA15" s="37" t="n"/>
       <c r="AB15" s="37" t="n"/>
@@ -39681,85 +39281,31 @@
       <c r="AR15" s="37" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="52" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B16" s="53" t="inlineStr">
-        <is>
-          <t>李涛</t>
-        </is>
-      </c>
-      <c r="C16" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D16" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E16" s="53" t="inlineStr">
-        <is>
-          <t>O1级学习顾问</t>
-        </is>
-      </c>
-      <c r="F16" s="54">
-        <f>G16+H16</f>
-        <v/>
-      </c>
-      <c r="G16" s="54" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H16" s="54">
-        <f>Q16+U16</f>
-        <v/>
-      </c>
-      <c r="I16" s="54" t="n">
-        <v>200000</v>
-      </c>
-      <c r="J16" s="54" t="n">
-        <v>200000</v>
-      </c>
-      <c r="K16" s="54" t="n">
-        <v>377200</v>
-      </c>
-      <c r="L16" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="54" t="n">
-        <v>2840.5</v>
-      </c>
-      <c r="N16" s="54" t="n">
-        <v>380040.5</v>
-      </c>
-      <c r="O16" s="55" t="n">
-        <v>1.9002025</v>
-      </c>
-      <c r="P16" s="55" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q16" s="62" t="n">
-        <v>7600.81</v>
-      </c>
-      <c r="R16" s="54" t="n"/>
-      <c r="S16" s="54" t="n"/>
-      <c r="T16" s="55" t="n"/>
-      <c r="U16" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="54" t="n">
-        <v>100</v>
-      </c>
-      <c r="W16" s="54" t="n">
-        <v>2000</v>
-      </c>
-      <c r="X16" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="54" t="n">
-        <v>2000</v>
-      </c>
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="37" t="n"/>
+      <c r="G16" s="37" t="n"/>
+      <c r="H16" s="37" t="n"/>
+      <c r="I16" s="37" t="n"/>
+      <c r="J16" s="37" t="n"/>
+      <c r="K16" s="37" t="n"/>
+      <c r="L16" s="37" t="n"/>
+      <c r="M16" s="37" t="n"/>
+      <c r="N16" s="37" t="n"/>
+      <c r="O16" s="37" t="n"/>
+      <c r="P16" s="37" t="n"/>
+      <c r="Q16" s="37" t="n"/>
+      <c r="R16" s="37" t="n"/>
+      <c r="S16" s="37" t="n"/>
+      <c r="T16" s="37" t="n"/>
+      <c r="U16" s="37" t="n"/>
+      <c r="V16" s="37" t="n"/>
+      <c r="W16" s="37" t="n"/>
+      <c r="X16" s="37" t="n"/>
+      <c r="Y16" s="37" t="n"/>
       <c r="Z16" s="37" t="n"/>
       <c r="AA16" s="37" t="n"/>
       <c r="AB16" s="37" t="n"/>
@@ -39781,85 +39327,31 @@
       <c r="AR16" s="37" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="52" t="n">
-        <v>45931</v>
-      </c>
-      <c r="B17" s="53" t="inlineStr">
-        <is>
-          <t>赵星火</t>
-        </is>
-      </c>
-      <c r="C17" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D17" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E17" s="53" t="inlineStr">
-        <is>
-          <t>O2级学习顾问</t>
-        </is>
-      </c>
-      <c r="F17" s="54">
-        <f>G17+H17</f>
-        <v/>
-      </c>
-      <c r="G17" s="54" t="n">
-        <v>600</v>
-      </c>
-      <c r="H17" s="54">
-        <f>Q17+U17</f>
-        <v/>
-      </c>
-      <c r="I17" s="54" t="n">
-        <v>670000</v>
-      </c>
-      <c r="J17" s="54" t="n">
-        <v>650000</v>
-      </c>
-      <c r="K17" s="54" t="n">
-        <v>937661.7</v>
-      </c>
-      <c r="L17" s="54" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M17" s="54" t="n">
-        <v>35003.13</v>
-      </c>
-      <c r="N17" s="54" t="n">
-        <v>972664.83</v>
-      </c>
-      <c r="O17" s="55" t="n">
-        <v>1.49640743076923</v>
-      </c>
-      <c r="P17" s="55" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q17" s="62" t="n">
-        <v>48633.2415</v>
-      </c>
-      <c r="R17" s="54" t="n"/>
-      <c r="S17" s="54" t="n"/>
-      <c r="T17" s="55" t="n"/>
-      <c r="U17" s="62" t="n">
-        <v>-138.9664</v>
-      </c>
-      <c r="V17" s="54" t="n">
-        <v>70</v>
-      </c>
-      <c r="W17" s="54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X17" s="55" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Y17" s="54" t="n">
-        <v>600</v>
-      </c>
+      <c r="A17" s="37" t="n"/>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="37" t="n"/>
+      <c r="G17" s="37" t="n"/>
+      <c r="H17" s="37" t="n"/>
+      <c r="I17" s="37" t="n"/>
+      <c r="J17" s="37" t="n"/>
+      <c r="K17" s="37" t="n"/>
+      <c r="L17" s="37" t="n"/>
+      <c r="M17" s="37" t="n"/>
+      <c r="N17" s="37" t="n"/>
+      <c r="O17" s="37" t="n"/>
+      <c r="P17" s="37" t="n"/>
+      <c r="Q17" s="37" t="n"/>
+      <c r="R17" s="37" t="n"/>
+      <c r="S17" s="37" t="n"/>
+      <c r="T17" s="37" t="n"/>
+      <c r="U17" s="37" t="n"/>
+      <c r="V17" s="37" t="n"/>
+      <c r="W17" s="37" t="n"/>
+      <c r="X17" s="37" t="n"/>
+      <c r="Y17" s="37" t="n"/>
       <c r="Z17" s="37" t="n"/>
       <c r="AA17" s="37" t="n"/>
       <c r="AB17" s="37" t="n"/>
@@ -39881,83 +39373,31 @@
       <c r="AR17" s="37" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="52" t="n">
-        <v>45931</v>
-      </c>
-      <c r="B18" s="53" t="inlineStr">
-        <is>
-          <t>谭悦</t>
-        </is>
-      </c>
-      <c r="C18" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D18" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E18" s="53" t="inlineStr">
-        <is>
-          <t>O3级学习顾问</t>
-        </is>
-      </c>
-      <c r="F18" s="54">
-        <f>G18+H18</f>
-        <v/>
-      </c>
-      <c r="G18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="54">
-        <f>Q18+U18</f>
-        <v/>
-      </c>
-      <c r="I18" s="54" t="n">
-        <v>670000</v>
-      </c>
-      <c r="J18" s="54" t="n">
-        <v>650000</v>
-      </c>
-      <c r="K18" s="54" t="n">
-        <v>1061471.4</v>
-      </c>
-      <c r="L18" s="54" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M18" s="54" t="n">
-        <v>59354.7</v>
-      </c>
-      <c r="N18" s="54" t="n">
-        <v>1120826.1</v>
-      </c>
-      <c r="O18" s="55" t="n">
-        <v>1.72434784615385</v>
-      </c>
-      <c r="P18" s="55" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q18" s="62" t="n">
-        <v>56041.305</v>
-      </c>
-      <c r="R18" s="54" t="n"/>
-      <c r="S18" s="54" t="n"/>
-      <c r="T18" s="55" t="n"/>
-      <c r="U18" s="62" t="n">
-        <v>-85.25239999999999</v>
-      </c>
-      <c r="V18" s="54" t="n">
-        <v>70</v>
-      </c>
-      <c r="W18" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="55" t="n"/>
-      <c r="Y18" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="A18" s="37" t="n"/>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="37" t="n"/>
+      <c r="G18" s="37" t="n"/>
+      <c r="H18" s="37" t="n"/>
+      <c r="I18" s="37" t="n"/>
+      <c r="J18" s="37" t="n"/>
+      <c r="K18" s="37" t="n"/>
+      <c r="L18" s="37" t="n"/>
+      <c r="M18" s="37" t="n"/>
+      <c r="N18" s="37" t="n"/>
+      <c r="O18" s="37" t="n"/>
+      <c r="P18" s="37" t="n"/>
+      <c r="Q18" s="37" t="n"/>
+      <c r="R18" s="37" t="n"/>
+      <c r="S18" s="37" t="n"/>
+      <c r="T18" s="37" t="n"/>
+      <c r="U18" s="37" t="n"/>
+      <c r="V18" s="37" t="n"/>
+      <c r="W18" s="37" t="n"/>
+      <c r="X18" s="37" t="n"/>
+      <c r="Y18" s="37" t="n"/>
       <c r="Z18" s="37" t="n"/>
       <c r="AA18" s="37" t="n"/>
       <c r="AB18" s="37" t="n"/>
@@ -39979,85 +39419,31 @@
       <c r="AR18" s="37" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="52" t="n">
-        <v>45931</v>
-      </c>
-      <c r="B19" s="53" t="inlineStr">
-        <is>
-          <t>李涛</t>
-        </is>
-      </c>
-      <c r="C19" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D19" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E19" s="53" t="inlineStr">
-        <is>
-          <t>O1级学习顾问</t>
-        </is>
-      </c>
-      <c r="F19" s="54">
-        <f>G19+H19</f>
-        <v/>
-      </c>
-      <c r="G19" s="54" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H19" s="54">
-        <f>Q19+U19</f>
-        <v/>
-      </c>
-      <c r="I19" s="54" t="n">
-        <v>345000</v>
-      </c>
-      <c r="J19" s="54" t="n">
-        <v>325000</v>
-      </c>
-      <c r="K19" s="54" t="n">
-        <v>516599</v>
-      </c>
-      <c r="L19" s="54" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M19" s="54" t="n">
-        <v>53229.38</v>
-      </c>
-      <c r="N19" s="54" t="n">
-        <v>569828.38</v>
-      </c>
-      <c r="O19" s="55" t="n">
-        <v>1.75331809230769</v>
-      </c>
-      <c r="P19" s="55" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q19" s="62" t="n">
-        <v>28491.419</v>
-      </c>
-      <c r="R19" s="54" t="n"/>
-      <c r="S19" s="54" t="n"/>
-      <c r="T19" s="55" t="n"/>
-      <c r="U19" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="54" t="n">
-        <v>70</v>
-      </c>
-      <c r="W19" s="54" t="n">
-        <v>2000</v>
-      </c>
-      <c r="X19" s="55" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Y19" s="54" t="n">
-        <v>1200</v>
-      </c>
+      <c r="A19" s="37" t="n"/>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="37" t="n"/>
+      <c r="H19" s="37" t="n"/>
+      <c r="I19" s="37" t="n"/>
+      <c r="J19" s="37" t="n"/>
+      <c r="K19" s="37" t="n"/>
+      <c r="L19" s="37" t="n"/>
+      <c r="M19" s="37" t="n"/>
+      <c r="N19" s="37" t="n"/>
+      <c r="O19" s="37" t="n"/>
+      <c r="P19" s="37" t="n"/>
+      <c r="Q19" s="37" t="n"/>
+      <c r="R19" s="37" t="n"/>
+      <c r="S19" s="37" t="n"/>
+      <c r="T19" s="37" t="n"/>
+      <c r="U19" s="37" t="n"/>
+      <c r="V19" s="37" t="n"/>
+      <c r="W19" s="37" t="n"/>
+      <c r="X19" s="37" t="n"/>
+      <c r="Y19" s="37" t="n"/>
       <c r="Z19" s="37" t="n"/>
       <c r="AA19" s="37" t="n"/>
       <c r="AB19" s="37" t="n"/>
@@ -40079,91 +39465,31 @@
       <c r="AR19" s="37" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="52" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B20" s="53" t="inlineStr">
-        <is>
-          <t>赵星火</t>
-        </is>
-      </c>
-      <c r="C20" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D20" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E20" s="53" t="inlineStr">
-        <is>
-          <t>学习顾问</t>
-        </is>
-      </c>
-      <c r="F20" s="54">
-        <f>G20+H20</f>
-        <v/>
-      </c>
-      <c r="G20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="54">
-        <f>Q20+U20</f>
-        <v/>
-      </c>
-      <c r="I20" s="54" t="n">
-        <v>408000</v>
-      </c>
-      <c r="J20" s="54" t="n">
-        <v>400000</v>
-      </c>
-      <c r="K20" s="54" t="n">
-        <v>808087.55</v>
-      </c>
-      <c r="L20" s="54" t="n">
-        <v>8000</v>
-      </c>
-      <c r="M20" s="54" t="n">
-        <v>71708.5</v>
-      </c>
-      <c r="N20" s="54" t="n">
-        <v>879796.05</v>
-      </c>
-      <c r="O20" s="55" t="n">
-        <v>2.199490125</v>
-      </c>
-      <c r="P20" s="55" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q20" s="62" t="n">
-        <v>43989.8025</v>
-      </c>
-      <c r="R20" s="54" t="n">
-        <v>20000</v>
-      </c>
-      <c r="S20" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="55" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="U20" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="54" t="n">
-        <v>40</v>
-      </c>
-      <c r="W20" s="54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X20" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="A20" s="37" t="n"/>
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="37" t="n"/>
+      <c r="H20" s="37" t="n"/>
+      <c r="I20" s="37" t="n"/>
+      <c r="J20" s="37" t="n"/>
+      <c r="K20" s="37" t="n"/>
+      <c r="L20" s="37" t="n"/>
+      <c r="M20" s="37" t="n"/>
+      <c r="N20" s="37" t="n"/>
+      <c r="O20" s="37" t="n"/>
+      <c r="P20" s="37" t="n"/>
+      <c r="Q20" s="37" t="n"/>
+      <c r="R20" s="37" t="n"/>
+      <c r="S20" s="37" t="n"/>
+      <c r="T20" s="37" t="n"/>
+      <c r="U20" s="37" t="n"/>
+      <c r="V20" s="37" t="n"/>
+      <c r="W20" s="37" t="n"/>
+      <c r="X20" s="37" t="n"/>
+      <c r="Y20" s="37" t="n"/>
       <c r="Z20" s="37" t="n"/>
       <c r="AA20" s="37" t="n"/>
       <c r="AB20" s="37" t="n"/>
@@ -40185,91 +39511,31 @@
       <c r="AR20" s="37" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="52" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B21" s="53" t="inlineStr">
-        <is>
-          <t>谭悦</t>
-        </is>
-      </c>
-      <c r="C21" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D21" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E21" s="53" t="inlineStr">
-        <is>
-          <t>学习顾问</t>
-        </is>
-      </c>
-      <c r="F21" s="54">
-        <f>G21+H21</f>
-        <v/>
-      </c>
-      <c r="G21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="54">
-        <f>Q21+U21</f>
-        <v/>
-      </c>
-      <c r="I21" s="54" t="n">
-        <v>378000</v>
-      </c>
-      <c r="J21" s="54" t="n">
-        <v>370000</v>
-      </c>
-      <c r="K21" s="54" t="n">
-        <v>1059668</v>
-      </c>
-      <c r="L21" s="54" t="n">
-        <v>8000</v>
-      </c>
-      <c r="M21" s="54" t="n">
-        <v>49468.2</v>
-      </c>
-      <c r="N21" s="54" t="n">
-        <v>1109136.2</v>
-      </c>
-      <c r="O21" s="55" t="n">
-        <v>2.93422275132275</v>
-      </c>
-      <c r="P21" s="55" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q21" s="62" t="n">
-        <v>55456.81</v>
-      </c>
-      <c r="R21" s="54" t="n">
-        <v>20000</v>
-      </c>
-      <c r="S21" s="54" t="n">
-        <v>40240.5</v>
-      </c>
-      <c r="T21" s="55" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="U21" s="62" t="n">
-        <v>80.48099999999999</v>
-      </c>
-      <c r="V21" s="54" t="n">
-        <v>100</v>
-      </c>
-      <c r="W21" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="A21" s="37" t="n"/>
+      <c r="B21" s="37" t="n"/>
+      <c r="C21" s="37" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="37" t="n"/>
+      <c r="G21" s="37" t="n"/>
+      <c r="H21" s="37" t="n"/>
+      <c r="I21" s="37" t="n"/>
+      <c r="J21" s="37" t="n"/>
+      <c r="K21" s="37" t="n"/>
+      <c r="L21" s="37" t="n"/>
+      <c r="M21" s="37" t="n"/>
+      <c r="N21" s="37" t="n"/>
+      <c r="O21" s="37" t="n"/>
+      <c r="P21" s="37" t="n"/>
+      <c r="Q21" s="37" t="n"/>
+      <c r="R21" s="37" t="n"/>
+      <c r="S21" s="37" t="n"/>
+      <c r="T21" s="37" t="n"/>
+      <c r="U21" s="37" t="n"/>
+      <c r="V21" s="37" t="n"/>
+      <c r="W21" s="37" t="n"/>
+      <c r="X21" s="37" t="n"/>
+      <c r="Y21" s="37" t="n"/>
       <c r="Z21" s="37" t="n"/>
       <c r="AA21" s="37" t="n"/>
       <c r="AB21" s="37" t="n"/>
@@ -40291,91 +39557,31 @@
       <c r="AR21" s="37" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="52" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B22" s="53" t="inlineStr">
-        <is>
-          <t>李涛</t>
-        </is>
-      </c>
-      <c r="C22" s="53" t="inlineStr">
-        <is>
-          <t>个性化</t>
-        </is>
-      </c>
-      <c r="D22" s="53" t="inlineStr">
-        <is>
-          <t>考研个性化</t>
-        </is>
-      </c>
-      <c r="E22" s="53" t="inlineStr">
-        <is>
-          <t>学习顾问</t>
-        </is>
-      </c>
-      <c r="F22" s="54">
-        <f>G22+H22</f>
-        <v/>
-      </c>
-      <c r="G22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="54">
-        <f>Q22+U22</f>
-        <v/>
-      </c>
-      <c r="I22" s="54" t="n">
-        <v>325000</v>
-      </c>
-      <c r="J22" s="54" t="n">
-        <v>320000</v>
-      </c>
-      <c r="K22" s="54" t="n">
-        <v>10078</v>
-      </c>
-      <c r="L22" s="54" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="54" t="n">
-        <v>10078</v>
-      </c>
-      <c r="O22" s="55" t="n">
-        <v>0.0310092307692308</v>
-      </c>
-      <c r="P22" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="54" t="n">
-        <v>20000</v>
-      </c>
-      <c r="S22" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="55" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="U22" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="54" t="n">
-        <v>60</v>
-      </c>
-      <c r="W22" s="54" t="n">
-        <v>2000</v>
-      </c>
-      <c r="X22" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="A22" s="37" t="n"/>
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="37" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="37" t="n"/>
+      <c r="G22" s="37" t="n"/>
+      <c r="H22" s="37" t="n"/>
+      <c r="I22" s="37" t="n"/>
+      <c r="J22" s="37" t="n"/>
+      <c r="K22" s="37" t="n"/>
+      <c r="L22" s="37" t="n"/>
+      <c r="M22" s="37" t="n"/>
+      <c r="N22" s="37" t="n"/>
+      <c r="O22" s="37" t="n"/>
+      <c r="P22" s="37" t="n"/>
+      <c r="Q22" s="37" t="n"/>
+      <c r="R22" s="37" t="n"/>
+      <c r="S22" s="37" t="n"/>
+      <c r="T22" s="37" t="n"/>
+      <c r="U22" s="37" t="n"/>
+      <c r="V22" s="37" t="n"/>
+      <c r="W22" s="37" t="n"/>
+      <c r="X22" s="37" t="n"/>
+      <c r="Y22" s="37" t="n"/>
       <c r="Z22" s="37" t="n"/>
       <c r="AA22" s="37" t="n"/>
       <c r="AB22" s="37" t="n"/>
@@ -40397,31 +39603,91 @@
       <c r="AR22" s="37" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="n"/>
-      <c r="B23" s="37" t="n"/>
-      <c r="C23" s="37" t="n"/>
-      <c r="D23" s="37" t="n"/>
-      <c r="E23" s="37" t="n"/>
-      <c r="F23" s="37" t="n"/>
-      <c r="G23" s="37" t="n"/>
-      <c r="H23" s="37" t="n"/>
-      <c r="I23" s="37" t="n"/>
-      <c r="J23" s="37" t="n"/>
-      <c r="K23" s="37" t="n"/>
-      <c r="L23" s="37" t="n"/>
-      <c r="M23" s="37" t="n"/>
-      <c r="N23" s="37" t="n"/>
-      <c r="O23" s="37" t="n"/>
-      <c r="P23" s="37" t="n"/>
-      <c r="Q23" s="37" t="n"/>
-      <c r="R23" s="37" t="n"/>
-      <c r="S23" s="37" t="n"/>
-      <c r="T23" s="37" t="n"/>
-      <c r="U23" s="37" t="n"/>
-      <c r="V23" s="37" t="n"/>
-      <c r="W23" s="37" t="n"/>
-      <c r="X23" s="37" t="n"/>
-      <c r="Y23" s="37" t="n"/>
+      <c r="A23" s="52" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B23" s="53" t="inlineStr">
+        <is>
+          <t>赵星火</t>
+        </is>
+      </c>
+      <c r="C23" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D23" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E23" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F23" s="54">
+        <f>G23+H23</f>
+        <v/>
+      </c>
+      <c r="G23" s="54" t="n">
+        <v>600</v>
+      </c>
+      <c r="H23" s="54">
+        <f>Q23+U23</f>
+        <v/>
+      </c>
+      <c r="I23" s="54" t="n">
+        <v>510000</v>
+      </c>
+      <c r="J23" s="54" t="n">
+        <v>500000</v>
+      </c>
+      <c r="K23" s="54" t="n">
+        <v>984542.6</v>
+      </c>
+      <c r="L23" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M23" s="54" t="n">
+        <v>5512.13</v>
+      </c>
+      <c r="N23" s="54" t="n">
+        <v>990054.73</v>
+      </c>
+      <c r="O23" s="55" t="n">
+        <v>1.98010946</v>
+      </c>
+      <c r="P23" s="55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q23" s="62" t="n">
+        <v>49502.7365</v>
+      </c>
+      <c r="R23" s="54" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S23" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="55" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="U23" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="54" t="n">
+        <v>70</v>
+      </c>
+      <c r="W23" s="54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X23" s="55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y23" s="54" t="n">
+        <v>600</v>
+      </c>
       <c r="Z23" s="37" t="n"/>
       <c r="AA23" s="37" t="n"/>
       <c r="AB23" s="37" t="n"/>
@@ -40443,31 +39709,89 @@
       <c r="AR23" s="37" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="n"/>
-      <c r="B24" s="37" t="n"/>
-      <c r="C24" s="37" t="n"/>
-      <c r="D24" s="37" t="n"/>
-      <c r="E24" s="37" t="n"/>
-      <c r="F24" s="37" t="n"/>
-      <c r="G24" s="37" t="n"/>
-      <c r="H24" s="37" t="n"/>
-      <c r="I24" s="37" t="n"/>
-      <c r="J24" s="37" t="n"/>
-      <c r="K24" s="37" t="n"/>
-      <c r="L24" s="37" t="n"/>
-      <c r="M24" s="37" t="n"/>
-      <c r="N24" s="37" t="n"/>
-      <c r="O24" s="37" t="n"/>
-      <c r="P24" s="37" t="n"/>
-      <c r="Q24" s="37" t="n"/>
-      <c r="R24" s="37" t="n"/>
-      <c r="S24" s="37" t="n"/>
-      <c r="T24" s="37" t="n"/>
-      <c r="U24" s="37" t="n"/>
-      <c r="V24" s="37" t="n"/>
-      <c r="W24" s="37" t="n"/>
-      <c r="X24" s="37" t="n"/>
-      <c r="Y24" s="37" t="n"/>
+      <c r="A24" s="52" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B24" s="53" t="inlineStr">
+        <is>
+          <t>李涛</t>
+        </is>
+      </c>
+      <c r="C24" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D24" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E24" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F24" s="54">
+        <f>G24+H24</f>
+        <v/>
+      </c>
+      <c r="G24" s="54" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H24" s="54">
+        <f>Q24+U24</f>
+        <v/>
+      </c>
+      <c r="I24" s="54" t="n">
+        <v>410000</v>
+      </c>
+      <c r="J24" s="54" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K24" s="54" t="n">
+        <v>49150</v>
+      </c>
+      <c r="L24" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M24" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="54" t="n">
+        <v>49150</v>
+      </c>
+      <c r="O24" s="55" t="n">
+        <v>0.119878048780488</v>
+      </c>
+      <c r="P24" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="54" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S24" s="54" t="n"/>
+      <c r="T24" s="55" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="U24" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="54" t="n">
+        <v>70</v>
+      </c>
+      <c r="W24" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X24" s="55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y24" s="54" t="n">
+        <v>1200</v>
+      </c>
       <c r="Z24" s="37" t="n"/>
       <c r="AA24" s="37" t="n"/>
       <c r="AB24" s="37" t="n"/>
@@ -40489,31 +39813,91 @@
       <c r="AR24" s="37" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="n"/>
-      <c r="B25" s="37" t="n"/>
-      <c r="C25" s="37" t="n"/>
-      <c r="D25" s="37" t="n"/>
-      <c r="E25" s="37" t="n"/>
-      <c r="F25" s="37" t="n"/>
-      <c r="G25" s="37" t="n"/>
-      <c r="H25" s="37" t="n"/>
-      <c r="I25" s="37" t="n"/>
-      <c r="J25" s="37" t="n"/>
-      <c r="K25" s="37" t="n"/>
-      <c r="L25" s="37" t="n"/>
-      <c r="M25" s="37" t="n"/>
-      <c r="N25" s="37" t="n"/>
-      <c r="O25" s="37" t="n"/>
-      <c r="P25" s="37" t="n"/>
-      <c r="Q25" s="37" t="n"/>
-      <c r="R25" s="37" t="n"/>
-      <c r="S25" s="37" t="n"/>
-      <c r="T25" s="37" t="n"/>
-      <c r="U25" s="37" t="n"/>
-      <c r="V25" s="37" t="n"/>
-      <c r="W25" s="37" t="n"/>
-      <c r="X25" s="37" t="n"/>
-      <c r="Y25" s="37" t="n"/>
+      <c r="A25" s="52" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B25" s="53" t="inlineStr">
+        <is>
+          <t>谭悦</t>
+        </is>
+      </c>
+      <c r="C25" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D25" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E25" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F25" s="54">
+        <f>G25+H25</f>
+        <v/>
+      </c>
+      <c r="G25" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="54">
+        <f>Q25+U25</f>
+        <v/>
+      </c>
+      <c r="I25" s="54" t="n">
+        <v>510000</v>
+      </c>
+      <c r="J25" s="54" t="n">
+        <v>500000</v>
+      </c>
+      <c r="K25" s="54" t="n">
+        <v>926563.65</v>
+      </c>
+      <c r="L25" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M25" s="54" t="n">
+        <v>188556.9</v>
+      </c>
+      <c r="N25" s="54" t="n">
+        <v>1115120.55</v>
+      </c>
+      <c r="O25" s="55" t="n">
+        <v>2.18651088235294</v>
+      </c>
+      <c r="P25" s="55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q25" s="62" t="n">
+        <v>55756.0275</v>
+      </c>
+      <c r="R25" s="54" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S25" s="54" t="n">
+        <v>71980</v>
+      </c>
+      <c r="T25" s="55" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="U25" s="62" t="n">
+        <v>143.96</v>
+      </c>
+      <c r="V25" s="54" t="n">
+        <v>100</v>
+      </c>
+      <c r="W25" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="Z25" s="37" t="n"/>
       <c r="AA25" s="37" t="n"/>
       <c r="AB25" s="37" t="n"/>
@@ -40535,31 +39919,89 @@
       <c r="AR25" s="37" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="n"/>
-      <c r="B26" s="37" t="n"/>
-      <c r="C26" s="37" t="n"/>
-      <c r="D26" s="37" t="n"/>
-      <c r="E26" s="37" t="n"/>
-      <c r="F26" s="37" t="n"/>
-      <c r="G26" s="37" t="n"/>
-      <c r="H26" s="37" t="n"/>
-      <c r="I26" s="37" t="n"/>
-      <c r="J26" s="37" t="n"/>
-      <c r="K26" s="37" t="n"/>
-      <c r="L26" s="37" t="n"/>
-      <c r="M26" s="37" t="n"/>
-      <c r="N26" s="37" t="n"/>
-      <c r="O26" s="37" t="n"/>
-      <c r="P26" s="37" t="n"/>
-      <c r="Q26" s="37" t="n"/>
-      <c r="R26" s="37" t="n"/>
-      <c r="S26" s="37" t="n"/>
-      <c r="T26" s="37" t="n"/>
-      <c r="U26" s="37" t="n"/>
-      <c r="V26" s="37" t="n"/>
-      <c r="W26" s="37" t="n"/>
-      <c r="X26" s="37" t="n"/>
-      <c r="Y26" s="37" t="n"/>
+      <c r="A26" s="52" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B26" s="53" t="inlineStr">
+        <is>
+          <t>谭悦</t>
+        </is>
+      </c>
+      <c r="C26" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D26" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E26" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F26" s="54">
+        <f>G26+H26</f>
+        <v/>
+      </c>
+      <c r="G26" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="54">
+        <f>Q26+U26</f>
+        <v/>
+      </c>
+      <c r="I26" s="54" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="J26" s="54" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="K26" s="54" t="n">
+        <v>3316276.2</v>
+      </c>
+      <c r="L26" s="54" t="n"/>
+      <c r="M26" s="54" t="n">
+        <v>76650.36</v>
+      </c>
+      <c r="N26" s="54" t="n">
+        <v>3316276.2</v>
+      </c>
+      <c r="O26" s="55" t="n">
+        <v>1.95075070588235</v>
+      </c>
+      <c r="P26" s="55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q26" s="62" t="n">
+        <v>166670.6136</v>
+      </c>
+      <c r="R26" s="54" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S26" s="54" t="n">
+        <v>249914</v>
+      </c>
+      <c r="T26" s="55" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="U26" s="62" t="n">
+        <v>499.828</v>
+      </c>
+      <c r="V26" s="54" t="n">
+        <v>100</v>
+      </c>
+      <c r="W26" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="Z26" s="37" t="n"/>
       <c r="AA26" s="37" t="n"/>
       <c r="AB26" s="37" t="n"/>
@@ -40581,31 +40023,89 @@
       <c r="AR26" s="37" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="37" t="n"/>
-      <c r="B27" s="37" t="n"/>
-      <c r="C27" s="37" t="n"/>
-      <c r="D27" s="37" t="n"/>
-      <c r="E27" s="37" t="n"/>
-      <c r="F27" s="37" t="n"/>
-      <c r="G27" s="37" t="n"/>
-      <c r="H27" s="37" t="n"/>
-      <c r="I27" s="37" t="n"/>
-      <c r="J27" s="37" t="n"/>
-      <c r="K27" s="37" t="n"/>
-      <c r="L27" s="37" t="n"/>
-      <c r="M27" s="37" t="n"/>
-      <c r="N27" s="37" t="n"/>
-      <c r="O27" s="37" t="n"/>
-      <c r="P27" s="37" t="n"/>
-      <c r="Q27" s="37" t="n"/>
-      <c r="R27" s="37" t="n"/>
-      <c r="S27" s="37" t="n"/>
-      <c r="T27" s="37" t="n"/>
-      <c r="U27" s="37" t="n"/>
-      <c r="V27" s="37" t="n"/>
-      <c r="W27" s="37" t="n"/>
-      <c r="X27" s="37" t="n"/>
-      <c r="Y27" s="37" t="n"/>
+      <c r="A27" s="52" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B27" s="53" t="inlineStr">
+        <is>
+          <t>赵星火</t>
+        </is>
+      </c>
+      <c r="C27" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D27" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E27" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F27" s="54">
+        <f>G27+H27</f>
+        <v/>
+      </c>
+      <c r="G27" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H27" s="54">
+        <f>Q27+U27</f>
+        <v/>
+      </c>
+      <c r="I27" s="54" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="J27" s="54" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="K27" s="54" t="n">
+        <v>2202125.4</v>
+      </c>
+      <c r="L27" s="54" t="n"/>
+      <c r="M27" s="54" t="n">
+        <v>101602.64</v>
+      </c>
+      <c r="N27" s="54" t="n">
+        <v>2202125.4</v>
+      </c>
+      <c r="O27" s="55" t="n">
+        <v>1.29536788235294</v>
+      </c>
+      <c r="P27" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q27" s="62" t="n">
+        <v>84165.4094</v>
+      </c>
+      <c r="R27" s="54" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S27" s="54" t="n">
+        <v>156831.2</v>
+      </c>
+      <c r="T27" s="55" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="U27" s="62" t="n">
+        <v>313.6624</v>
+      </c>
+      <c r="V27" s="54" t="n">
+        <v>100</v>
+      </c>
+      <c r="W27" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X27" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="54" t="n">
+        <v>2000</v>
+      </c>
       <c r="Z27" s="37" t="n"/>
       <c r="AA27" s="37" t="n"/>
       <c r="AB27" s="37" t="n"/>
@@ -40627,31 +40127,89 @@
       <c r="AR27" s="37" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="n"/>
-      <c r="B28" s="37" t="n"/>
-      <c r="C28" s="37" t="n"/>
-      <c r="D28" s="37" t="n"/>
-      <c r="E28" s="37" t="n"/>
-      <c r="F28" s="37" t="n"/>
-      <c r="G28" s="37" t="n"/>
-      <c r="H28" s="37" t="n"/>
-      <c r="I28" s="37" t="n"/>
-      <c r="J28" s="37" t="n"/>
-      <c r="K28" s="37" t="n"/>
-      <c r="L28" s="37" t="n"/>
-      <c r="M28" s="37" t="n"/>
-      <c r="N28" s="37" t="n"/>
-      <c r="O28" s="37" t="n"/>
-      <c r="P28" s="37" t="n"/>
-      <c r="Q28" s="37" t="n"/>
-      <c r="R28" s="37" t="n"/>
-      <c r="S28" s="37" t="n"/>
-      <c r="T28" s="37" t="n"/>
-      <c r="U28" s="37" t="n"/>
-      <c r="V28" s="37" t="n"/>
-      <c r="W28" s="37" t="n"/>
-      <c r="X28" s="37" t="n"/>
-      <c r="Y28" s="37" t="n"/>
+      <c r="A28" s="52" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B28" s="53" t="inlineStr">
+        <is>
+          <t>李涛</t>
+        </is>
+      </c>
+      <c r="C28" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D28" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E28" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F28" s="54">
+        <f>G28+H28</f>
+        <v/>
+      </c>
+      <c r="G28" s="54" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H28" s="54">
+        <f>Q28+U28</f>
+        <v/>
+      </c>
+      <c r="I28" s="54" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J28" s="54" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="K28" s="54" t="n">
+        <v>1643589.8</v>
+      </c>
+      <c r="L28" s="54" t="n"/>
+      <c r="M28" s="54" t="n">
+        <v>18661.2</v>
+      </c>
+      <c r="N28" s="54" t="n">
+        <v>1643589.8</v>
+      </c>
+      <c r="O28" s="55" t="n">
+        <v>1.09572653333333</v>
+      </c>
+      <c r="P28" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q28" s="62" t="n">
+        <v>47494.306</v>
+      </c>
+      <c r="R28" s="54" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S28" s="54" t="n">
+        <v>86600</v>
+      </c>
+      <c r="T28" s="55" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="U28" s="62" t="n">
+        <v>173.2</v>
+      </c>
+      <c r="V28" s="54" t="n">
+        <v>100</v>
+      </c>
+      <c r="W28" s="54" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X28" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="54" t="n">
+        <v>4000</v>
+      </c>
       <c r="Z28" s="37" t="n"/>
       <c r="AA28" s="37" t="n"/>
       <c r="AB28" s="37" t="n"/>
@@ -40673,31 +40231,77 @@
       <c r="AR28" s="37" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="n"/>
-      <c r="B29" s="37" t="n"/>
-      <c r="C29" s="37" t="n"/>
-      <c r="D29" s="37" t="n"/>
-      <c r="E29" s="37" t="n"/>
-      <c r="F29" s="37" t="n"/>
-      <c r="G29" s="37" t="n"/>
-      <c r="H29" s="37" t="n"/>
-      <c r="I29" s="37" t="n"/>
-      <c r="J29" s="37" t="n"/>
-      <c r="K29" s="37" t="n"/>
-      <c r="L29" s="37" t="n"/>
-      <c r="M29" s="37" t="n"/>
-      <c r="N29" s="37" t="n"/>
-      <c r="O29" s="37" t="n"/>
-      <c r="P29" s="37" t="n"/>
-      <c r="Q29" s="37" t="n"/>
-      <c r="R29" s="37" t="n"/>
-      <c r="S29" s="37" t="n"/>
-      <c r="T29" s="37" t="n"/>
-      <c r="U29" s="37" t="n"/>
-      <c r="V29" s="37" t="n"/>
-      <c r="W29" s="37" t="n"/>
-      <c r="X29" s="37" t="n"/>
-      <c r="Y29" s="37" t="n"/>
+      <c r="A29" s="52" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B29" s="53" t="inlineStr">
+        <is>
+          <t>王志鹏</t>
+        </is>
+      </c>
+      <c r="C29" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D29" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E29" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F29" s="54">
+        <f>G29+H29</f>
+        <v/>
+      </c>
+      <c r="G29" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H29" s="54">
+        <f>Q29+U29</f>
+        <v/>
+      </c>
+      <c r="I29" s="54" t="n"/>
+      <c r="J29" s="54" t="n"/>
+      <c r="K29" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="54" t="n"/>
+      <c r="M29" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="55" t="n"/>
+      <c r="P29" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="54" t="n"/>
+      <c r="S29" s="54" t="n"/>
+      <c r="T29" s="55" t="n"/>
+      <c r="U29" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="54" t="n">
+        <v>70</v>
+      </c>
+      <c r="W29" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X29" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="54" t="n">
+        <v>2000</v>
+      </c>
       <c r="Z29" s="37" t="n"/>
       <c r="AA29" s="37" t="n"/>
       <c r="AB29" s="37" t="n"/>
@@ -40719,31 +40323,89 @@
       <c r="AR29" s="37" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="37" t="n"/>
-      <c r="B30" s="37" t="n"/>
-      <c r="C30" s="37" t="n"/>
-      <c r="D30" s="37" t="n"/>
-      <c r="E30" s="37" t="n"/>
-      <c r="F30" s="37" t="n"/>
-      <c r="G30" s="37" t="n"/>
-      <c r="H30" s="37" t="n"/>
-      <c r="I30" s="37" t="n"/>
-      <c r="J30" s="37" t="n"/>
-      <c r="K30" s="37" t="n"/>
-      <c r="L30" s="37" t="n"/>
-      <c r="M30" s="37" t="n"/>
-      <c r="N30" s="37" t="n"/>
-      <c r="O30" s="37" t="n"/>
-      <c r="P30" s="37" t="n"/>
-      <c r="Q30" s="37" t="n"/>
-      <c r="R30" s="37" t="n"/>
-      <c r="S30" s="37" t="n"/>
-      <c r="T30" s="37" t="n"/>
-      <c r="U30" s="37" t="n"/>
-      <c r="V30" s="37" t="n"/>
-      <c r="W30" s="37" t="n"/>
-      <c r="X30" s="37" t="n"/>
-      <c r="Y30" s="37" t="n"/>
+      <c r="A30" s="52" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B30" s="53" t="inlineStr">
+        <is>
+          <t>谭悦</t>
+        </is>
+      </c>
+      <c r="C30" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D30" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E30" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F30" s="54">
+        <f>G30+H30</f>
+        <v/>
+      </c>
+      <c r="G30" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="54">
+        <f>Q30+U30</f>
+        <v/>
+      </c>
+      <c r="I30" s="54" t="n">
+        <v>670000</v>
+      </c>
+      <c r="J30" s="54" t="n">
+        <v>670000</v>
+      </c>
+      <c r="K30" s="54" t="n">
+        <v>1258888.55</v>
+      </c>
+      <c r="L30" s="54" t="n"/>
+      <c r="M30" s="54" t="n">
+        <v>18902.3</v>
+      </c>
+      <c r="N30" s="54" t="n">
+        <v>1258888.55</v>
+      </c>
+      <c r="O30" s="55" t="n">
+        <v>1.87893813432836</v>
+      </c>
+      <c r="P30" s="55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q30" s="62" t="n">
+        <v>63133.4505</v>
+      </c>
+      <c r="R30" s="54" t="n">
+        <v>50000</v>
+      </c>
+      <c r="S30" s="54" t="n">
+        <v>11000</v>
+      </c>
+      <c r="T30" s="55" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="U30" s="62" t="n">
+        <v>-22</v>
+      </c>
+      <c r="V30" s="54" t="n">
+        <v>70</v>
+      </c>
+      <c r="W30" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y30" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="Z30" s="37" t="n"/>
       <c r="AA30" s="37" t="n"/>
       <c r="AB30" s="37" t="n"/>
@@ -40765,31 +40427,89 @@
       <c r="AR30" s="37" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="n"/>
-      <c r="B31" s="37" t="n"/>
-      <c r="C31" s="37" t="n"/>
-      <c r="D31" s="37" t="n"/>
-      <c r="E31" s="37" t="n"/>
-      <c r="F31" s="37" t="n"/>
-      <c r="G31" s="37" t="n"/>
-      <c r="H31" s="37" t="n"/>
-      <c r="I31" s="37" t="n"/>
-      <c r="J31" s="37" t="n"/>
-      <c r="K31" s="37" t="n"/>
-      <c r="L31" s="37" t="n"/>
-      <c r="M31" s="37" t="n"/>
-      <c r="N31" s="37" t="n"/>
-      <c r="O31" s="37" t="n"/>
-      <c r="P31" s="37" t="n"/>
-      <c r="Q31" s="37" t="n"/>
-      <c r="R31" s="37" t="n"/>
-      <c r="S31" s="37" t="n"/>
-      <c r="T31" s="37" t="n"/>
-      <c r="U31" s="37" t="n"/>
-      <c r="V31" s="37" t="n"/>
-      <c r="W31" s="37" t="n"/>
-      <c r="X31" s="37" t="n"/>
-      <c r="Y31" s="37" t="n"/>
+      <c r="A31" s="52" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B31" s="53" t="inlineStr">
+        <is>
+          <t>赵星火</t>
+        </is>
+      </c>
+      <c r="C31" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D31" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E31" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F31" s="54">
+        <f>G31+H31</f>
+        <v/>
+      </c>
+      <c r="G31" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="54">
+        <f>Q31+U31</f>
+        <v/>
+      </c>
+      <c r="I31" s="54" t="n">
+        <v>670000</v>
+      </c>
+      <c r="J31" s="54" t="n">
+        <v>670000</v>
+      </c>
+      <c r="K31" s="54" t="n">
+        <v>418685.6</v>
+      </c>
+      <c r="L31" s="54" t="n"/>
+      <c r="M31" s="54" t="n">
+        <v>28670.35</v>
+      </c>
+      <c r="N31" s="54" t="n">
+        <v>418685.6</v>
+      </c>
+      <c r="O31" s="55" t="n">
+        <v>0.624903880597015</v>
+      </c>
+      <c r="P31" s="55" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="Q31" s="62" t="n">
+        <v>3636.1883</v>
+      </c>
+      <c r="R31" s="54" t="n">
+        <v>50000</v>
+      </c>
+      <c r="S31" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="55" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="U31" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="54" t="n">
+        <v>19.5945945945946</v>
+      </c>
+      <c r="W31" s="54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X31" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="Z31" s="37" t="n"/>
       <c r="AA31" s="37" t="n"/>
       <c r="AB31" s="37" t="n"/>
@@ -40811,31 +40531,89 @@
       <c r="AR31" s="37" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="37" t="n"/>
-      <c r="B32" s="37" t="n"/>
-      <c r="C32" s="37" t="n"/>
-      <c r="D32" s="37" t="n"/>
-      <c r="E32" s="37" t="n"/>
-      <c r="F32" s="37" t="n"/>
-      <c r="G32" s="37" t="n"/>
-      <c r="H32" s="37" t="n"/>
-      <c r="I32" s="37" t="n"/>
-      <c r="J32" s="37" t="n"/>
-      <c r="K32" s="37" t="n"/>
-      <c r="L32" s="37" t="n"/>
-      <c r="M32" s="37" t="n"/>
-      <c r="N32" s="37" t="n"/>
-      <c r="O32" s="37" t="n"/>
-      <c r="P32" s="37" t="n"/>
-      <c r="Q32" s="37" t="n"/>
-      <c r="R32" s="37" t="n"/>
-      <c r="S32" s="37" t="n"/>
-      <c r="T32" s="37" t="n"/>
-      <c r="U32" s="37" t="n"/>
-      <c r="V32" s="37" t="n"/>
-      <c r="W32" s="37" t="n"/>
-      <c r="X32" s="37" t="n"/>
-      <c r="Y32" s="37" t="n"/>
+      <c r="A32" s="52" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B32" s="53" t="inlineStr">
+        <is>
+          <t>李涛</t>
+        </is>
+      </c>
+      <c r="C32" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D32" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E32" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F32" s="54">
+        <f>G32+H32</f>
+        <v/>
+      </c>
+      <c r="G32" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="54">
+        <f>Q32+U32</f>
+        <v/>
+      </c>
+      <c r="I32" s="54" t="n">
+        <v>630000</v>
+      </c>
+      <c r="J32" s="54" t="n">
+        <v>630000</v>
+      </c>
+      <c r="K32" s="54" t="n">
+        <v>8366.79999999999</v>
+      </c>
+      <c r="L32" s="54" t="n"/>
+      <c r="M32" s="54" t="n">
+        <v>1199.1</v>
+      </c>
+      <c r="N32" s="54" t="n">
+        <v>8366.79999999999</v>
+      </c>
+      <c r="O32" s="55" t="n">
+        <v>0.0132806349206349</v>
+      </c>
+      <c r="P32" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="62" t="n">
+        <v>11.991</v>
+      </c>
+      <c r="R32" s="54" t="n">
+        <v>40000</v>
+      </c>
+      <c r="S32" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="55" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="U32" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="54" t="n">
+        <v>11.9565217391304</v>
+      </c>
+      <c r="W32" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X32" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="Z32" s="37" t="n"/>
       <c r="AA32" s="37" t="n"/>
       <c r="AB32" s="37" t="n"/>
@@ -40857,31 +40635,83 @@
       <c r="AR32" s="37" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="n"/>
-      <c r="B33" s="37" t="n"/>
-      <c r="C33" s="37" t="n"/>
-      <c r="D33" s="37" t="n"/>
-      <c r="E33" s="37" t="n"/>
-      <c r="F33" s="37" t="n"/>
-      <c r="G33" s="37" t="n"/>
-      <c r="H33" s="37" t="n"/>
-      <c r="I33" s="37" t="n"/>
-      <c r="J33" s="37" t="n"/>
-      <c r="K33" s="37" t="n"/>
-      <c r="L33" s="37" t="n"/>
-      <c r="M33" s="37" t="n"/>
-      <c r="N33" s="37" t="n"/>
-      <c r="O33" s="37" t="n"/>
-      <c r="P33" s="37" t="n"/>
-      <c r="Q33" s="37" t="n"/>
-      <c r="R33" s="37" t="n"/>
-      <c r="S33" s="37" t="n"/>
-      <c r="T33" s="37" t="n"/>
-      <c r="U33" s="37" t="n"/>
-      <c r="V33" s="37" t="n"/>
-      <c r="W33" s="37" t="n"/>
-      <c r="X33" s="37" t="n"/>
-      <c r="Y33" s="37" t="n"/>
+      <c r="A33" s="52" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B33" s="53" t="inlineStr">
+        <is>
+          <t>王志鹏</t>
+        </is>
+      </c>
+      <c r="C33" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D33" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E33" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F33" s="54">
+        <f>G33+H33</f>
+        <v/>
+      </c>
+      <c r="G33" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H33" s="54">
+        <f>Q33+U33</f>
+        <v/>
+      </c>
+      <c r="I33" s="54" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J33" s="54" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K33" s="54" t="n">
+        <v>98971.2</v>
+      </c>
+      <c r="L33" s="54" t="n"/>
+      <c r="M33" s="54" t="n">
+        <v>8971.200000000001</v>
+      </c>
+      <c r="N33" s="54" t="n">
+        <v>107942.4</v>
+      </c>
+      <c r="O33" s="55" t="n">
+        <v>3.59808</v>
+      </c>
+      <c r="P33" s="55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q33" s="62" t="n">
+        <v>2248.56</v>
+      </c>
+      <c r="R33" s="54" t="n"/>
+      <c r="S33" s="54" t="n"/>
+      <c r="T33" s="55" t="n"/>
+      <c r="U33" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="54" t="n">
+        <v>70</v>
+      </c>
+      <c r="W33" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X33" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="54" t="n">
+        <v>2000</v>
+      </c>
       <c r="Z33" s="37" t="n"/>
       <c r="AA33" s="37" t="n"/>
       <c r="AB33" s="37" t="n"/>
@@ -40903,31 +40733,91 @@
       <c r="AR33" s="37" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="37" t="n"/>
-      <c r="B34" s="37" t="n"/>
-      <c r="C34" s="37" t="n"/>
-      <c r="D34" s="37" t="n"/>
-      <c r="E34" s="37" t="n"/>
-      <c r="F34" s="37" t="n"/>
-      <c r="G34" s="37" t="n"/>
-      <c r="H34" s="37" t="n"/>
-      <c r="I34" s="37" t="n"/>
-      <c r="J34" s="37" t="n"/>
-      <c r="K34" s="37" t="n"/>
-      <c r="L34" s="37" t="n"/>
-      <c r="M34" s="37" t="n"/>
-      <c r="N34" s="37" t="n"/>
-      <c r="O34" s="37" t="n"/>
-      <c r="P34" s="37" t="n"/>
-      <c r="Q34" s="37" t="n"/>
-      <c r="R34" s="37" t="n"/>
-      <c r="S34" s="37" t="n"/>
-      <c r="T34" s="37" t="n"/>
-      <c r="U34" s="37" t="n"/>
-      <c r="V34" s="37" t="n"/>
-      <c r="W34" s="37" t="n"/>
-      <c r="X34" s="37" t="n"/>
-      <c r="Y34" s="37" t="n"/>
+      <c r="A34" s="52" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B34" s="53" t="inlineStr">
+        <is>
+          <t>谭悦</t>
+        </is>
+      </c>
+      <c r="C34" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D34" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E34" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F34" s="54">
+        <f>G34+H34</f>
+        <v/>
+      </c>
+      <c r="G34" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="54">
+        <f>Q34+U34</f>
+        <v/>
+      </c>
+      <c r="I34" s="54" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J34" s="54" t="n">
+        <v>600000</v>
+      </c>
+      <c r="K34" s="54" t="n">
+        <v>1227260.25</v>
+      </c>
+      <c r="L34" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="54" t="n">
+        <v>-8019.2</v>
+      </c>
+      <c r="N34" s="54" t="n">
+        <v>1227260.25</v>
+      </c>
+      <c r="O34" s="55" t="n">
+        <v>2.04543375</v>
+      </c>
+      <c r="P34" s="55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q34" s="62" t="n">
+        <v>61282.8205</v>
+      </c>
+      <c r="R34" s="54" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S34" s="54" t="n">
+        <v>288079.2</v>
+      </c>
+      <c r="T34" s="55" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="U34" s="62" t="n">
+        <v>576.1584</v>
+      </c>
+      <c r="V34" s="54" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="W34" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="Z34" s="37" t="n"/>
       <c r="AA34" s="37" t="n"/>
       <c r="AB34" s="37" t="n"/>
@@ -40949,31 +40839,91 @@
       <c r="AR34" s="37" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="n"/>
-      <c r="B35" s="37" t="n"/>
-      <c r="C35" s="37" t="n"/>
-      <c r="D35" s="37" t="n"/>
-      <c r="E35" s="37" t="n"/>
-      <c r="F35" s="37" t="n"/>
-      <c r="G35" s="37" t="n"/>
-      <c r="H35" s="37" t="n"/>
-      <c r="I35" s="37" t="n"/>
-      <c r="J35" s="37" t="n"/>
-      <c r="K35" s="37" t="n"/>
-      <c r="L35" s="37" t="n"/>
-      <c r="M35" s="37" t="n"/>
-      <c r="N35" s="37" t="n"/>
-      <c r="O35" s="37" t="n"/>
-      <c r="P35" s="37" t="n"/>
-      <c r="Q35" s="37" t="n"/>
-      <c r="R35" s="37" t="n"/>
-      <c r="S35" s="37" t="n"/>
-      <c r="T35" s="37" t="n"/>
-      <c r="U35" s="37" t="n"/>
-      <c r="V35" s="37" t="n"/>
-      <c r="W35" s="37" t="n"/>
-      <c r="X35" s="37" t="n"/>
-      <c r="Y35" s="37" t="n"/>
+      <c r="A35" s="52" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B35" s="53" t="inlineStr">
+        <is>
+          <t>赵星火</t>
+        </is>
+      </c>
+      <c r="C35" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D35" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E35" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F35" s="54">
+        <f>G35+H35</f>
+        <v/>
+      </c>
+      <c r="G35" s="54" t="n">
+        <v>906</v>
+      </c>
+      <c r="H35" s="54">
+        <f>Q35+U35</f>
+        <v/>
+      </c>
+      <c r="I35" s="54" t="n">
+        <v>652000</v>
+      </c>
+      <c r="J35" s="54" t="n">
+        <v>652000</v>
+      </c>
+      <c r="K35" s="54" t="n">
+        <v>917528</v>
+      </c>
+      <c r="L35" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="54" t="n">
+        <v>9585</v>
+      </c>
+      <c r="N35" s="54" t="n">
+        <v>917528</v>
+      </c>
+      <c r="O35" s="55" t="n">
+        <v>1.40725153374233</v>
+      </c>
+      <c r="P35" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q35" s="62" t="n">
+        <v>36796.97</v>
+      </c>
+      <c r="R35" s="54" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S35" s="54" t="n">
+        <v>95090.8</v>
+      </c>
+      <c r="T35" s="55" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="U35" s="62" t="n">
+        <v>190.1816</v>
+      </c>
+      <c r="V35" s="54" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="W35" s="54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X35" s="55" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="Y35" s="54" t="n">
+        <v>906</v>
+      </c>
       <c r="Z35" s="37" t="n"/>
       <c r="AA35" s="37" t="n"/>
       <c r="AB35" s="37" t="n"/>
@@ -40995,31 +40945,91 @@
       <c r="AR35" s="37" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="37" t="n"/>
-      <c r="B36" s="37" t="n"/>
-      <c r="C36" s="37" t="n"/>
-      <c r="D36" s="37" t="n"/>
-      <c r="E36" s="37" t="n"/>
-      <c r="F36" s="37" t="n"/>
-      <c r="G36" s="37" t="n"/>
-      <c r="H36" s="37" t="n"/>
-      <c r="I36" s="37" t="n"/>
-      <c r="J36" s="37" t="n"/>
-      <c r="K36" s="37" t="n"/>
-      <c r="L36" s="37" t="n"/>
-      <c r="M36" s="37" t="n"/>
-      <c r="N36" s="37" t="n"/>
-      <c r="O36" s="37" t="n"/>
-      <c r="P36" s="37" t="n"/>
-      <c r="Q36" s="37" t="n"/>
-      <c r="R36" s="37" t="n"/>
-      <c r="S36" s="37" t="n"/>
-      <c r="T36" s="37" t="n"/>
-      <c r="U36" s="37" t="n"/>
-      <c r="V36" s="37" t="n"/>
-      <c r="W36" s="37" t="n"/>
-      <c r="X36" s="37" t="n"/>
-      <c r="Y36" s="37" t="n"/>
+      <c r="A36" s="52" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B36" s="53" t="inlineStr">
+        <is>
+          <t>李涛</t>
+        </is>
+      </c>
+      <c r="C36" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D36" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E36" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F36" s="54">
+        <f>G36+H36</f>
+        <v/>
+      </c>
+      <c r="G36" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="54">
+        <f>Q36+U36</f>
+        <v/>
+      </c>
+      <c r="I36" s="54" t="n">
+        <v>612000</v>
+      </c>
+      <c r="J36" s="54" t="n">
+        <v>612000</v>
+      </c>
+      <c r="K36" s="54" t="n">
+        <v>875815.5</v>
+      </c>
+      <c r="L36" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="54" t="n">
+        <v>875815.5</v>
+      </c>
+      <c r="O36" s="55" t="n">
+        <v>1.43107107843137</v>
+      </c>
+      <c r="P36" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q36" s="62" t="n">
+        <v>35032.62</v>
+      </c>
+      <c r="R36" s="54" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S36" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="55" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="U36" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="54" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="W36" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X36" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="Z36" s="37" t="n"/>
       <c r="AA36" s="37" t="n"/>
       <c r="AB36" s="37" t="n"/>
@@ -41041,31 +41051,91 @@
       <c r="AR36" s="37" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="37" t="n"/>
-      <c r="B37" s="37" t="n"/>
-      <c r="C37" s="37" t="n"/>
-      <c r="D37" s="37" t="n"/>
-      <c r="E37" s="37" t="n"/>
-      <c r="F37" s="37" t="n"/>
-      <c r="G37" s="37" t="n"/>
-      <c r="H37" s="37" t="n"/>
-      <c r="I37" s="37" t="n"/>
-      <c r="J37" s="37" t="n"/>
-      <c r="K37" s="37" t="n"/>
-      <c r="L37" s="37" t="n"/>
-      <c r="M37" s="37" t="n"/>
-      <c r="N37" s="37" t="n"/>
-      <c r="O37" s="37" t="n"/>
-      <c r="P37" s="37" t="n"/>
-      <c r="Q37" s="37" t="n"/>
-      <c r="R37" s="37" t="n"/>
-      <c r="S37" s="37" t="n"/>
-      <c r="T37" s="37" t="n"/>
-      <c r="U37" s="37" t="n"/>
-      <c r="V37" s="37" t="n"/>
-      <c r="W37" s="37" t="n"/>
-      <c r="X37" s="37" t="n"/>
-      <c r="Y37" s="37" t="n"/>
+      <c r="A37" s="52" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B37" s="53" t="inlineStr">
+        <is>
+          <t>王志鹏</t>
+        </is>
+      </c>
+      <c r="C37" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D37" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E37" s="53" t="inlineStr">
+        <is>
+          <t>学习顾问</t>
+        </is>
+      </c>
+      <c r="F37" s="54">
+        <f>G37+H37</f>
+        <v/>
+      </c>
+      <c r="G37" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H37" s="54">
+        <f>Q37+U37</f>
+        <v/>
+      </c>
+      <c r="I37" s="54" t="n">
+        <v>156000</v>
+      </c>
+      <c r="J37" s="54" t="n">
+        <v>156000</v>
+      </c>
+      <c r="K37" s="54" t="n">
+        <v>158001.55</v>
+      </c>
+      <c r="L37" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="54" t="n">
+        <v>3410.4</v>
+      </c>
+      <c r="N37" s="54" t="n">
+        <v>158001.55</v>
+      </c>
+      <c r="O37" s="55" t="n">
+        <v>1.01283044871795</v>
+      </c>
+      <c r="P37" s="55" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Q37" s="62" t="n">
+        <v>1930.1226</v>
+      </c>
+      <c r="R37" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="55" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="U37" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="54" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="W37" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X37" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="54" t="n">
+        <v>2000</v>
+      </c>
       <c r="Z37" s="37" t="n"/>
       <c r="AA37" s="37" t="n"/>
       <c r="AB37" s="37" t="n"/>
